--- a/data/trans_dic/P19C06-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C06-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,83</t>
+          <t>0,28; 2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,21</t>
+          <t>0,51; 2,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,32</t>
+          <t>0,25; 2,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,17</t>
+          <t>0,24; 2,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,32</t>
+          <t>0,24; 2,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,52</t>
+          <t>0,28; 2,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,95</t>
+          <t>0,39; 1,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,94</t>
+          <t>0,4; 1,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,95</t>
+          <t>0,42; 1,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,52</t>
+          <t>0,23; 3,51</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,7</t>
+          <t>0,19; 1,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,09</t>
+          <t>0,31; 2,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,76</t>
+          <t>0,39; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,0</t>
+          <t>0,19; 1,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,15</t>
+          <t>0,21; 2,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,64</t>
+          <t>0,58; 2,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,5</t>
+          <t>0,33; 2,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,35</t>
+          <t>0,28; 1,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,67</t>
+          <t>0,39; 1,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,16</t>
+          <t>0,67; 2,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,79</t>
+          <t>0,41; 1,77</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,95</t>
+          <t>0,2; 1,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,35</t>
+          <t>0,49; 2,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,9</t>
+          <t>0,24; 1,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,6</t>
+          <t>0,66; 2,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,98</t>
+          <t>1,47; 4,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,23</t>
+          <t>0,32; 2,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,61</t>
+          <t>0,29; 1,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,92</t>
+          <t>0,62; 1,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,71</t>
+          <t>1,23; 2,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,69</t>
+          <t>0,41; 1,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,93</t>
+          <t>0,18; 0,92</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,24</t>
+          <t>0,39; 3,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,2</t>
+          <t>0,41; 3,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,77</t>
+          <t>0,21; 1,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,96</t>
+          <t>1,09; 3,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,31</t>
+          <t>0,79; 3,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,1</t>
+          <t>0,39; 2,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,73</t>
+          <t>0,98; 2,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,22</t>
+          <t>0,77; 2,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,61</t>
+          <t>0,81; 2,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,09</t>
+          <t>0,57; 2,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,91</t>
+          <t>0,65; 1,92</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,71</t>
+          <t>1,02; 4,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,35</t>
+          <t>0,27; 2,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,44</t>
+          <t>0,58; 3,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,16</t>
+          <t>0,48; 2,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,24</t>
+          <t>0,53; 2,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,05</t>
+          <t>1,12; 4,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,49</t>
+          <t>0,85; 2,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,86</t>
+          <t>0,72; 2,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,21</t>
+          <t>0,43; 2,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,47</t>
+          <t>1,16; 3,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,97</t>
+          <t>0,8; 1,96</t>
         </is>
       </c>
     </row>
@@ -1417,37 +1417,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,16</t>
+          <t>0,43; 3,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,41</t>
+          <t>0,45; 4,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,24</t>
+          <t>0,34; 2,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,47</t>
+          <t>0,29; 2,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,06</t>
+          <t>0,37; 3,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,32</t>
+          <t>0,39; 2,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,98</t>
+          <t>0,33; 1,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,65</t>
+          <t>0,61; 2,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,43</t>
+          <t>0,31; 1,38</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,56</t>
+          <t>0,76; 8,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,43</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,02</t>
+          <t>0,36; 3,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,99</t>
+          <t>0,53; 5,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,63</t>
+          <t>0,32; 1,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,68</t>
+          <t>0,33; 3,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,85</t>
+          <t>0,22; 1,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,74</t>
+          <t>0,6; 3,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,2</t>
+          <t>0,3; 1,18</t>
         </is>
       </c>
     </row>
@@ -1697,57 +1697,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,56</t>
+          <t>0,76; 1,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,48</t>
+          <t>0,66; 1,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,73</t>
+          <t>0,77; 1,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,33</t>
+          <t>0,53; 1,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,57</t>
+          <t>0,79; 1,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,96</t>
+          <t>1,05; 1,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,83</t>
+          <t>0,96; 1,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,41</t>
+          <t>0,76; 1,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,45</t>
+          <t>0,85; 1,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,52</t>
+          <t>0,97; 1,59</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,59</t>
+          <t>0,99; 1,59</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1000; 10171</t>
+          <t>996; 10086</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1920; 12183</t>
+          <t>1918; 11017</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>892; 8169</t>
+          <t>888; 8129</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 24661</t>
+          <t>0; 25026</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>902; 8183</t>
+          <t>904; 9044</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>881; 8622</t>
+          <t>893; 7909</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>972; 8857</t>
+          <t>984; 8834</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 8102</t>
+          <t>0; 9082</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2908; 14368</t>
+          <t>2880; 14136</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3054; 14534</t>
+          <t>2995; 13904</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2956; 13767</t>
+          <t>2962; 14057</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1576; 24186</t>
+          <t>1567; 24109</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1084; 9778</t>
+          <t>1099; 9214</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1784; 12495</t>
+          <t>1856; 12520</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1975; 13624</t>
+          <t>1901; 12748</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 10922</t>
+          <t>0; 9264</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1011; 10931</t>
+          <t>1023; 9905</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1044; 11991</t>
+          <t>1166; 11596</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2834; 13110</t>
+          <t>2891; 13223</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1574; 12486</t>
+          <t>1648; 11724</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3814; 15181</t>
+          <t>3133; 15199</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4590; 19305</t>
+          <t>4510; 19388</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6574; 21410</t>
+          <t>6627; 20461</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3209; 16154</t>
+          <t>3724; 15994</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1011; 9819</t>
+          <t>1024; 9074</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2995; 13758</t>
+          <t>2880; 14535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1030; 10617</t>
+          <t>1327; 10931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4931</t>
+          <t>0; 6252</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4022; 15668</t>
+          <t>3977; 15681</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9643; 26173</t>
+          <t>9653; 26444</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1950; 12770</t>
+          <t>1813; 11832</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1490; 8581</t>
+          <t>1558; 8368</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6986; 21285</t>
+          <t>6846; 20944</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14718; 33751</t>
+          <t>15299; 34856</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4634; 19142</t>
+          <t>4682; 18124</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1904; 9827</t>
+          <t>1866; 9672</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5906</t>
+          <t>0; 5975</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2134; 17612</t>
+          <t>2102; 16276</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2188; 16374</t>
+          <t>2092; 15399</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2222; 15237</t>
+          <t>1841; 16227</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4814; 17375</t>
+          <t>4774; 16872</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4759; 18674</t>
+          <t>4445; 18748</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2094; 11468</t>
+          <t>2109; 11774</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6720; 19104</t>
+          <t>6892; 18587</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5777; 18717</t>
+          <t>6467; 20151</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9240; 28893</t>
+          <t>8909; 28768</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6245; 22129</t>
+          <t>6043; 21832</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10796; 29898</t>
+          <t>10194; 30096</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2848; 12825</t>
+          <t>2770; 12570</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>974; 8503</t>
+          <t>966; 7983</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2073; 16490</t>
+          <t>2167; 14490</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2466; 11816</t>
+          <t>2620; 12421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 9059</t>
+          <t>0; 10264</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2108; 12653</t>
+          <t>2058; 11516</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4445; 16047</t>
+          <t>4445; 17125</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4652; 13287</t>
+          <t>4541; 12908</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4537; 16889</t>
+          <t>4263; 16795</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4086; 16629</t>
+          <t>3258; 15426</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8667; 26644</t>
+          <t>8865; 25044</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8716; 21261</t>
+          <t>8671; 21241</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>911; 8842</t>
+          <t>909; 8116</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6159</t>
+          <t>0; 6873</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1026; 10150</t>
+          <t>1042; 10686</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1122; 8056</t>
+          <t>1230; 7840</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6001</t>
+          <t>0; 5649</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>893; 7413</t>
+          <t>885; 7325</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1006; 8464</t>
+          <t>1018; 8462</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>904; 8841</t>
+          <t>914; 8791</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1760; 10656</t>
+          <t>1799; 11486</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1878; 11122</t>
+          <t>1833; 10743</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3006; 13440</t>
+          <t>3083; 14412</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3068; 13714</t>
+          <t>2956; 13215</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>952; 9585</t>
+          <t>961; 10279</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2137</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7981</t>
+          <t>0; 5430</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4241</t>
+          <t>0; 4492</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5335</t>
+          <t>0; 5260</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1095; 9135</t>
+          <t>1089; 10179</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1231; 11375</t>
+          <t>1198; 11953</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1377; 6648</t>
+          <t>1307; 6671</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1127; 12316</t>
+          <t>1121; 11525</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1095; 8994</t>
+          <t>1087; 9047</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2361; 14039</t>
+          <t>2236; 13238</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1956; 8185</t>
+          <t>2061; 8096</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18164; 38256</t>
+          <t>18548; 38698</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20054; 43082</t>
+          <t>19176; 43009</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21809; 46014</t>
+          <t>20435; 45366</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16831; 44629</t>
+          <t>17637; 47547</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>21919; 43006</t>
+          <t>21592; 42782</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33303; 61523</t>
+          <t>32881; 60713</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25919; 52492</t>
+          <t>27394; 51842</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27131; 50506</t>
+          <t>27140; 49962</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>44581; 75159</t>
+          <t>43972; 74330</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>57445; 91903</t>
+          <t>58938; 96114</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>53556; 87748</t>
+          <t>54526; 88150</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>49680; 87707</t>
+          <t>50028; 88190</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C06-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C06-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,81</t>
+          <t>0,28; 2,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,91</t>
+          <t>0,5; 2,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,3</t>
+          <t>0,25; 2,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,53</t>
+          <t>0,0; 4,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,4</t>
+          <t>0,47; 2,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,13</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,51</t>
+          <t>0,28; 2,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,92</t>
+          <t>0,44; 1,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,85</t>
+          <t>0,49; 1,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,99</t>
+          <t>0,41; 1,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,51</t>
+          <t>0,19; 2,42</t>
         </is>
       </c>
     </row>
@@ -804,14 +804,14 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,6</t>
+          <t>0,19; 1,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,1</t>
+          <t>0,31; 2,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,59</t>
+          <t>0,4; 2,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,81</t>
+          <t>0,18; 1,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,08</t>
+          <t>0,21; 2,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,66</t>
+          <t>0,58; 2,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,35</t>
+          <t>0,35; 2,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,35</t>
+          <t>0,34; 1,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,68</t>
+          <t>0,41; 1,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,07</t>
+          <t>0,65; 2,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,77</t>
+          <t>0,35; 1,65</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,8</t>
+          <t>0,2; 1,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,48</t>
+          <t>0,5; 2,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,96</t>
+          <t>0,18; 1,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,6</t>
+          <t>0,65; 2,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,02</t>
+          <t>1,47; 4,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,06</t>
+          <t>0,33; 2,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,57</t>
+          <t>0,34; 1,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,89</t>
+          <t>0,62; 2,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,8</t>
+          <t>1,19; 2,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,6</t>
+          <t>0,39; 1,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,92</t>
+          <t>0,21; 1,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,0</t>
+          <t>0,41; 2,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,01</t>
+          <t>0,41; 3,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,88</t>
+          <t>0,39; 2,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,84</t>
+          <t>1,09; 3,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,33</t>
+          <t>0,97; 3,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,16</t>
+          <t>0,39; 2,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,65</t>
+          <t>0,92; 2,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,39</t>
+          <t>0,75; 2,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,6</t>
+          <t>0,83; 2,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,06</t>
+          <t>0,6; 2,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,92</t>
+          <t>0,83; 2,04</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,62</t>
+          <t>1,02; 4,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,21</t>
+          <t>0,27; 2,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,91</t>
+          <t>0,56; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,27</t>
+          <t>0,46; 2,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,95</t>
+          <t>0,52; 2,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,33</t>
+          <t>1,13; 4,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,41</t>
+          <t>0,84; 2,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,84</t>
+          <t>0,79; 2,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,05</t>
+          <t>0,54; 2,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,27</t>
+          <t>1,12; 3,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,96</t>
+          <t>0,77; 1,8</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,81</t>
+          <t>0,43; 4,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,64</t>
+          <t>0,44; 4,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,18</t>
+          <t>0,32; 2,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,44</t>
+          <t>0,29; 2,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,06</t>
+          <t>0,37; 3,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,47</t>
+          <t>0,48; 1,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,5</t>
+          <t>0,38; 2,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,91</t>
+          <t>0,33; 1,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,84</t>
+          <t>0,61; 2,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,38</t>
+          <t>0,55; 1,7</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,11</t>
+          <t>0,75; 7,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,52 +1567,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,37</t>
+          <t>0,36; 3,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,25</t>
+          <t>0,53; 5,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,63</t>
+          <t>0,29; 1,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,44</t>
+          <t>0,34; 3,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,86</t>
+          <t>0,22; 2,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,53</t>
+          <t>0,65; 3,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,18</t>
+          <t>0,29; 1,06</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,58</t>
+          <t>0,73; 1,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,48</t>
+          <t>0,66; 1,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,7</t>
+          <t>0,78; 1,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,42</t>
+          <t>0,49; 1,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,56</t>
+          <t>0,79; 1,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,93</t>
+          <t>1,03; 1,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,81</t>
+          <t>0,95; 1,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,4</t>
+          <t>0,86; 1,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,43</t>
+          <t>0,86; 1,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,59</t>
+          <t>0,95; 1,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,59</t>
+          <t>1,0; 1,63</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,27</t>
+          <t>0,75; 1,17</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>5953</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>996; 10086</t>
+          <t>1004; 9755</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1918; 11017</t>
+          <t>1887; 10619</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>888; 8129</t>
+          <t>892; 8177</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 25026</t>
+          <t>0; 15541</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>904; 9044</t>
+          <t>1757; 9148</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>893; 7909</t>
+          <t>0; 7744</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>984; 8834</t>
+          <t>981; 9728</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9082</t>
+          <t>0; 11755</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2880; 14136</t>
+          <t>3220; 14594</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2995; 13904</t>
+          <t>3688; 14515</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2962; 14057</t>
+          <t>2922; 13943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1567; 24109</t>
+          <t>1382; 17476</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7689</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1099; 9214</t>
+          <t>1072; 10081</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1856; 12520</t>
+          <t>1838; 11923</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1901; 12748</t>
+          <t>1973; 12674</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 9264</t>
+          <t>0; 8909</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1023; 9905</t>
+          <t>992; 9869</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1166; 11596</t>
+          <t>1169; 12357</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2891; 13223</t>
+          <t>2869; 13420</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1648; 11724</t>
+          <t>1685; 10727</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3133; 15199</t>
+          <t>3801; 14319</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4510; 19388</t>
+          <t>4695; 19068</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6627; 20461</t>
+          <t>6413; 21550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3724; 15994</t>
+          <t>3222; 15341</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5859</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1024; 9074</t>
+          <t>1006; 9202</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2880; 14535</t>
+          <t>2934; 14418</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1327; 10931</t>
+          <t>1024; 10520</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6252</t>
+          <t>0; 6126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3977; 15681</t>
+          <t>3940; 16727</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9653; 26444</t>
+          <t>9693; 27157</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1813; 11832</t>
+          <t>1918; 13934</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1558; 8368</t>
+          <t>2082; 10264</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6846; 20944</t>
+          <t>6849; 22602</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15299; 34856</t>
+          <t>14767; 33683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4682; 18124</t>
+          <t>4395; 17802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1866; 9672</t>
+          <t>2523; 12097</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>18905</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5975</t>
+          <t>0; 6204</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2102; 16276</t>
+          <t>2237; 15909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2092; 15399</t>
+          <t>2082; 15657</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1841; 16227</t>
+          <t>2664; 15944</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4774; 16872</t>
+          <t>4785; 17055</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4445; 18748</t>
+          <t>5447; 19426</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2109; 11774</t>
+          <t>2105; 12004</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6892; 18587</t>
+          <t>6656; 17767</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6467; 20151</t>
+          <t>6289; 19530</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8909; 28768</t>
+          <t>9234; 27858</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6043; 21832</t>
+          <t>6342; 21931</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10194; 30096</t>
+          <t>11681; 28603</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>14725</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2770; 12570</t>
+          <t>2782; 13222</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>966; 7983</t>
+          <t>974; 9274</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2167; 14490</t>
+          <t>2073; 15262</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2620; 12421</t>
+          <t>2725; 12342</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 10264</t>
+          <t>0; 9526</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2058; 11516</t>
+          <t>2051; 11548</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4445; 17125</t>
+          <t>4485; 17897</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4541; 12908</t>
+          <t>4992; 14112</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4263; 16795</t>
+          <t>4695; 17485</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3258; 15426</t>
+          <t>4083; 16925</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8865; 25044</t>
+          <t>8585; 25994</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8671; 21241</t>
+          <t>9206; 21348</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>8177</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>909; 8116</t>
+          <t>913; 8826</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6873</t>
+          <t>0; 6685</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1042; 10686</t>
+          <t>1020; 9276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1230; 7840</t>
+          <t>1274; 8015</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5649</t>
+          <t>0; 6175</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>885; 7325</t>
+          <t>885; 7594</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1018; 8462</t>
+          <t>1016; 9513</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>914; 8791</t>
+          <t>2065; 8516</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1799; 11486</t>
+          <t>1768; 10357</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1833; 10743</t>
+          <t>1875; 10621</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3083; 14412</t>
+          <t>3094; 14296</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2956; 13215</t>
+          <t>4511; 14029</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4509</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>961; 10279</t>
+          <t>949; 10065</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3326,52 +3326,52 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5430</t>
+          <t>0; 6161</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4492</t>
+          <t>0; 3606</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5260</t>
+          <t>0; 5599</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1089; 10179</t>
+          <t>1089; 9424</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1198; 11953</t>
+          <t>1205; 12099</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1307; 6671</t>
+          <t>1277; 6351</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1121; 11525</t>
+          <t>1134; 10959</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1087; 9047</t>
+          <t>1088; 9958</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2236; 13238</t>
+          <t>2440; 14389</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2061; 8096</t>
+          <t>2182; 7967</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>37773</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>65599</t>
+          <t>65816</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18548; 38698</t>
+          <t>17947; 39477</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19176; 43009</t>
+          <t>19331; 42640</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20435; 45366</t>
+          <t>20681; 46112</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17637; 47547</t>
+          <t>16717; 38755</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>21592; 42782</t>
+          <t>21766; 43025</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32881; 60713</t>
+          <t>32266; 60387</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27394; 51842</t>
+          <t>27304; 51039</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27140; 49962</t>
+          <t>31072; 51186</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43972; 74330</t>
+          <t>44777; 75670</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>58938; 96114</t>
+          <t>57838; 91307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>54526; 88150</t>
+          <t>55441; 89976</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>50028; 88190</t>
+          <t>52408; 82327</t>
         </is>
       </c>
     </row>
